--- a/server/ATS/template/srms_allpassed_template.xlsx
+++ b/server/ATS/template/srms_allpassed_template.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63769673-CF3C-4B0E-AC11-D5C7B103B725}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7A5DB76-3885-4782-938D-73341F1E5504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -906,7 +906,7 @@
     <col min="2" max="2" width="24.5546875" customWidth="1"/>
     <col min="3" max="3" width="10.88671875" customWidth="1"/>
     <col min="4" max="4" width="14.6640625" customWidth="1"/>
-    <col min="5" max="5" width="30.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.5546875" customWidth="1"/>
     <col min="6" max="6" width="12.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
